--- a/Testcase.xlsx
+++ b/Testcase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\งานเก้ง\Test software\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21FFCD86-2266-434A-AD10-AE9BD8ABB741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF8AA259-0704-48D0-B574-B8CD92D1C417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{934BA05D-BEB4-4009-B15C-471D19DFCA2B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="102">
   <si>
     <t>รหัส</t>
   </si>
@@ -239,12 +239,6 @@
     <t>Date = ว่าง</t>
   </si>
   <si>
-    <t>ใส่วันที่ผิด format</t>
-  </si>
-  <si>
-    <t>error format</t>
-  </si>
-  <si>
     <t>ใส่ special char comment</t>
   </si>
   <si>
@@ -336,6 +330,18 @@
   </si>
   <si>
     <t>Username : sss  Password : sss</t>
+  </si>
+  <si>
+    <t>จองวันที่ย้อนหลัง</t>
+  </si>
+  <si>
+    <t>ไม่สามารถจองย้อนหลังได้</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ไม่สามารถจองได้ </t>
+  </si>
+  <si>
+    <t>ควรเพิ่มแค่อันเดียว</t>
   </si>
 </sst>
 </file>
@@ -367,7 +373,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -440,40 +446,64 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -809,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70FE6C91-9D36-439E-BFB6-938DAFF1CBC5}">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.875" customWidth="1"/>
@@ -818,568 +848,560 @@
     <col min="4" max="4" width="18.625" customWidth="1"/>
     <col min="5" max="5" width="15.75" customWidth="1"/>
     <col min="6" max="6" width="18.875" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="7" max="7" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="8"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="4"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="10"/>
-    </row>
-    <row r="4" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="D5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="10" t="s">
+      <c r="D6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="10"/>
-    </row>
-    <row r="5" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="F6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="10"/>
-    </row>
-    <row r="6" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="F7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="9"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="11"/>
+    </row>
+    <row r="12" spans="1:7" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="14">
+        <v>46381</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A22" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="10"/>
-    </row>
-    <row r="7" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="C25" s="14">
+        <v>46016</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="10"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="10">
-        <v>46386</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="10"/>
-    </row>
-    <row r="21" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="10"/>
-    </row>
-    <row r="22" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="10"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="10"/>
-    </row>
-    <row r="24" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
+      <c r="E25" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="B26" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="10"/>
-    </row>
-    <row r="25" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="10">
-        <v>46016</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="G25" s="10"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" s="10"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="G27" s="10"/>
+      <c r="G27" s="5" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" s="9"/>
+      <c r="A40" s="1"/>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" s="9"/>
+      <c r="A41" s="1"/>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" s="9"/>
+      <c r="A42" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
